--- a/runs/RELX/2026-10-14/bear/scratch/b_margin_331/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_margin_331/out/dcf.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BEAR SCRATCH (bear/run_bear.py): brief bear_agent_margin. Base value was 0.35; base source: PM decision 14 Oct 2026, briefs/RELX.yaml dcf.base_margin: H1 2026 adjusted operating margin without print (1,727 - 78) / (4,871 - 157) = 35.0% (RELX H1 2026 interim results 6-K ex 99.1 (accession 0000929869-26-000054, 23 Jul 2026, https://www.sec.gov/Archives/edgar/data/929869/000092986926000054/relx-20260723xex99d1.htm) p.1-9). Data agent check: FY25 adjusted margin 3,342 / 9,590 = 34.85% incl. print (AR25 p.186).</t>
+          <t>BEAR SCRATCH (bear/run_bear.py): old bear_agent_margin, FY23 group incl. print. Base value was 0.35; base source: PM decision 14 Oct 2026, briefs/RELX.yaml dcf.base_margin: H1 2026 adjusted operating margin without print (1,727 - 78) / (4,871 - 157) = 35.0% (RELX H1 2026 interim results 6-K ex 99.1 (accession 0000929869-26-000054, 23 Jul 2026, https://www.sec.gov/Archives/edgar/data/929869/000092986926000054/relx-20260723xex99d1.htm) p.1-9). Data agent check: FY25 adjusted margin 3,342 / 9,590 = 34.85% incl. print (AR25 p.186).</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1928.347977986037</v>
+        <v>1982.999106946482</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>10497.46848467244</v>
+        <v>10656.78658211307</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>35824.00212354615</v>
+        <v>39335.57824653413</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>23714.25487158918</v>
+        <v>26776.76035998699</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>34211.72335626162</v>
+        <v>37433.54694210006</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>27214.72335626162</v>
+        <v>30436.54694210006</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>26117.44551636522</v>
+        <v>29415.00898307034</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>14.97770593075228</v>
+        <v>16.86877662759181</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1497.770593075228</v>
+        <v>1686.877662759181</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4594837268</v>
+        <v>-0.3912386637</v>
       </c>
     </row>
   </sheetData>
